--- a/Assets/GameSample/Forms/Excels/Story/Scene/MapObject_MapBase.xlsx
+++ b/Assets/GameSample/Forms/Excels/Story/Scene/MapObject_MapBase.xlsx
@@ -1222,9 +1222,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1238,6 +1238,8 @@
     <col min="9" max="9" width="13.65" style="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="38" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1277,6 +1279,14 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="str">
+        <v>boundsCollision</v>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">centerCollider</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1314,6 +1324,14 @@
       </c>
       <c r="L2" t="s">
         <v>16</v>
+      </c>
+      <c r="M2" t="str">
+        <v>write</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">write</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1351,6 +1369,14 @@
       <c r="L3" t="s">
         <v>28</v>
       </c>
+      <c r="M3" t="str">
+        <v>贴图边界碰撞</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碰撞体居中</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
@@ -1389,6 +1415,14 @@
       <c r="L4" t="s">
         <v>32</v>
       </c>
+      <c r="M4" t="str">
+        <v>bool</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bool</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2">
@@ -1402,12 +1436,20 @@
       </c>
       <c r="L5">
         <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="H6" s="2"/>
+      <c r="M6"/>
+      <c r="N6"/>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2"/>
@@ -1415,6 +1457,8 @@
       <c r="C7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="2"/>
+      <c r="M7"/>
+      <c r="N7"/>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2"/>
@@ -1422,6 +1466,8 @@
       <c r="C8" s="2"/>
       <c r="E8" s="2"/>
       <c r="H8" s="2"/>
+      <c r="M8"/>
+      <c r="N8"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2"/>
@@ -1429,6 +1475,8 @@
       <c r="C9" s="2"/>
       <c r="E9" s="2"/>
       <c r="H9" s="2"/>
+      <c r="M9"/>
+      <c r="N9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
